--- a/results/04_model_execution_2025_holdout/04_model_execution_2025_holdout.xlsx
+++ b/results/04_model_execution_2025_holdout/04_model_execution_2025_holdout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table_of_Contents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Section_5A_Master_Model_Executi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_of_Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section_5A_Master_Model_Executi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Section_5A_Master_Model_Executi'!$A$1:$J$7</definedName>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>10</v>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -668,233 +668,159 @@
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>M0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Deterministic Baseline</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Diurnal Seasonal Naive (y_{t-24})</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>1748.2</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>1420.1</v>
-      </c>
-      <c r="F2" s="10" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baseline Control</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Diurnal Volatility Naive (y_{t-24})</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>685.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>310.4</v>
+      </c>
+      <c r="F2" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G2" s="10" t="n">
-        <v>939.8</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>1377.3</v>
-      </c>
-      <c r="I2" s="11" t="n">
+      <c r="G2" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="11" t="n">
-        <v>0.4508</v>
+      <c r="J2" t="n">
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M1*</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Deterministic Baseline</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Contemporaneous Sched SARIMAX</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>1421.5</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>1180.4</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>-327.4</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>1042.6</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>1393.8</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>1.109</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>0.4375</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deterministic Schedule Bank Volatility Baseline</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>643</v>
+      </c>
+      <c r="E3" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-42.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.498</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Probabilistic / ML</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Convolved Lead Flights Only</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>1452.8</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>1395.2</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>-296.8</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>856.2</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>1195.5</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>0.5862000000000001</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Supervised Volatility GBR (Combined Values + Vol)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>668.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>178</v>
+      </c>
+      <c r="H4" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6178</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Probabilistic / ML</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Convolved Lead + OTP Delays/Cancels</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>1454.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1398.7</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>-295.3</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>855.1</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>1192.9</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0.588</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dynamic Hybrid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sequential SARIMA-Tree Volatility Hybrid</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7483</v>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Probabilistic / ML</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Full Tri-Modal Pipeline (LF Int)</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1318.8</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>1412</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>-430.8</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>856.3</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>1208.6</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>0.5770999999999999</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Dynamic Hybrid Model</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Sequential SARIMA-Tree Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1346.7</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1489.3</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>-402.9</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>795</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1135</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>0.627</v>
-      </c>
-    </row>
+    <row r="6" ht="19" customHeight="1"/>
+    <row r="7" ht="19" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/04_model_execution_2025_holdout/04_model_execution_2025_holdout.xlsx
+++ b/results/04_model_execution_2025_holdout/04_model_execution_2025_holdout.xlsx
@@ -670,7 +670,7 @@
     <row r="2" ht="19" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>Baseline Control</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diurnal Volatility Naive (y_{t-24})</t>
+          <t>Daily Persistence Benchmark (y_{t-24})</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -708,17 +708,17 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M1*</t>
+          <t>Model 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deterministic Baseline</t>
+          <t>Deterministic Schedule</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deterministic Schedule Bank Volatility Baseline</t>
+          <t>Deterministic Flight Schedule Model (convolved show-up curve)</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -746,17 +746,17 @@
     <row r="4" ht="19" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>Model 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Probabilistic / ML</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Supervised Volatility GBR (Combined Values + Vol)</t>
+          <t>Supervised Machine Learning Model (Decision Trees &amp; OTP)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -784,7 +784,7 @@
     <row r="5" ht="19" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>Model 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sequential SARIMA-Tree Volatility Hybrid</t>
+          <t>Dynamic Two-Stage Hybrid Model (Schedule + Real-time feedback)</t>
         </is>
       </c>
       <c r="D5" t="n">
